--- a/data/curriculum_mapping.xlsx
+++ b/data/curriculum_mapping.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\박준철\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\박준철\Desktop\임승원(20241101~)\20260915_chat-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4B0172B-0DA6-460B-B291-CD5926183FB3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0F5A1A6-7696-464B-A5E6-3C773BA8449E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="139">
   <si>
     <t>전공명</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -482,6 +482,46 @@
   </si>
   <si>
     <t>55. 첨단소재공학 마이크로디그리.PNG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스마트영양관리 MD</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>정신건강 사회복지 MD</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>56. 정신건강 사회복지 마이크로디그리.PNG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>커뮤니티 케어 MD</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>57. 커뮤니티 케어 마이크로디그리.PNG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>식생활안전관리 MD</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>58. 식생활안전관리 마이크로디그리.PNG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>59. 스마트영양관리 마이크로디그리.PNG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GX 융합디자이너 MD</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>60. GX 융합디자이너 마이크로디그리.PNG</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -835,7 +875,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C63"/>
+  <dimension ref="A1:C68"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="34.5" bestFit="1" customWidth="1"/>
@@ -1536,6 +1576,61 @@
         <v>128</v>
       </c>
     </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A64" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C64" s="5" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A65" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C65" s="5" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A66" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A67" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C67" s="5" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A68" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C68" s="5" t="s">
+        <v>138</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/curriculum_mapping.xlsx
+++ b/data/curriculum_mapping.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\박준철\Desktop\임승원(20241101~)\20260915_chat-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0F5A1A6-7696-464B-A5E6-3C773BA8449E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62159CC8-FAEA-4AE9-AD55-AE4D71DB8D79}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -473,10 +473,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>53 귀금속보석공예 마이크로디그리.PNG</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>54. 최신반도체공정 마이크로디그리.PNG</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -522,6 +518,10 @@
   </si>
   <si>
     <t>60. GX 융합디자이너 마이크로디그리.PNG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>53. 귀금속보석공예 마이크로디그리.PNG</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1551,7 +1551,7 @@
         <v>39</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
@@ -1562,7 +1562,7 @@
         <v>39</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
@@ -1573,62 +1573,62 @@
         <v>39</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C64" s="5" t="s">
         <v>130</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C64" s="5" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C65" s="5" t="s">
         <v>132</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C65" s="5" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C66" s="5" t="s">
         <v>134</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C66" s="5" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C68" s="5" t="s">
         <v>137</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C68" s="5" t="s">
-        <v>138</v>
       </c>
     </row>
   </sheetData>
